--- a/GF_X-master/AAAGameData/Languages/English.xlsx
+++ b/GF_X-master/AAAGameData/Languages/English.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,38 +34,35 @@
   <commentList>
     <comment ref="A1" authorId="0">
       <text>
-        <r>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
           <rPr>
             <sz val="11"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
           </rPr>
-          <t>勾选锁定此行,锁定后将强制保留</t>
-        </r>
+          <t xml:space="preserve">勾选锁定此行,锁定后将强制保留</t>
+        </d:r>
       </text>
     </comment>
     <comment ref="B1" authorId="0">
       <text>
-        <r>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
           <rPr>
             <sz val="11"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
           </rPr>
-          <t>多语言Key</t>
-        </r>
+          <t xml:space="preserve">多语言Key</t>
+        </d:r>
       </text>
     </comment>
     <comment ref="C1" authorId="0">
       <text>
-        <r>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
           <rPr>
             <sz val="11"/>
             <rFont val="Calibri"/>
-            <charset val="134"/>
           </rPr>
-          <t>多语言Value, 当值为空时, [一键翻译]会自动填充Value值</t>
-        </r>
+          <t xml:space="preserve">多语言Value, 当值为空时, [一键翻译]会自动填充Value值</t>
+        </d:r>
       </text>
     </comment>
   </commentList>
@@ -78,211 +75,211 @@
     <t>BRAKE</t>
   </si>
   <si>
-    <t>brake</t>
+    <t>刹车</t>
   </si>
   <si>
     <t>ENGINE</t>
   </si>
   <si>
-    <t>engine</t>
+    <t>引擎</t>
   </si>
   <si>
     <t>FailGame</t>
   </si>
   <si>
-    <t>You were discovered by your boss and immediately fired, living on the streets from then on. Click to start over and reverse time</t>
+    <t>你被老板发现，立刻被开除了，从此流落街头，点击重来逆转时间</t>
   </si>
   <si>
     <t>GET</t>
   </si>
   <si>
-    <t>obtain</t>
+    <t>获取</t>
   </si>
   <si>
     <t>Level.DisplayName1</t>
   </si>
   <si>
-    <t>Level 1 Name</t>
+    <t>关卡1名字</t>
   </si>
   <si>
     <t>Level.DisplayName2</t>
   </si>
   <si>
-    <t>Level 2 Name</t>
+    <t>关卡2名字</t>
   </si>
   <si>
     <t>Level.DisplayName3</t>
   </si>
   <si>
-    <t>Level 3 Name</t>
+    <t>关卡3名字</t>
   </si>
   <si>
     <t>Level.DisplayName4</t>
   </si>
   <si>
-    <t>Level 4 Name</t>
+    <t>关卡4名字</t>
   </si>
   <si>
     <t>Level.DisplayName5</t>
   </si>
   <si>
-    <t>Level 5 Name</t>
+    <t>关卡5名字</t>
   </si>
   <si>
     <t>MenuUIForm.Tips</t>
   </si>
   <si>
-    <t>Click to start</t>
+    <t>点击开始</t>
   </si>
   <si>
     <t>Nice</t>
   </si>
   <si>
-    <t>Well done!</t>
+    <t>干得漂亮！</t>
   </si>
   <si>
     <t>Nothing</t>
   </si>
   <si>
-    <t>Not implemented</t>
+    <t>未实现</t>
   </si>
   <si>
     <t>OFF</t>
   </si>
   <si>
-    <t>shut</t>
+    <t>关</t>
   </si>
   <si>
     <t>ON</t>
   </si>
   <si>
-    <t>open</t>
+    <t>开</t>
   </si>
   <si>
     <t>RatingDialog.CancelTxt</t>
   </si>
   <si>
-    <t>cancel</t>
+    <t>取消</t>
   </si>
   <si>
     <t>RatingDialog.HighRatingTips</t>
   </si>
   <si>
-    <t>Thank you for your affirmation! We will continue to work hard!</t>
+    <t>感谢您的肯定! 我们将再接再厉!</t>
   </si>
   <si>
     <t>RatingDialog.LowRatingTips</t>
   </si>
   <si>
-    <t>Thank you for your evaluation. We will do our best to improve and optimize it!</t>
+    <t>感谢您的评价,我们尽力完善优化!</t>
   </si>
   <si>
     <t>RatingDialog.RateTxt</t>
   </si>
   <si>
-    <t>Star rating</t>
+    <t>评星</t>
   </si>
   <si>
     <t>RETRY</t>
   </si>
   <si>
-    <t>retry</t>
+    <t>重试</t>
   </si>
   <si>
     <t>REVIVE</t>
   </si>
   <si>
-    <t>resurrection</t>
+    <t>复活</t>
   </si>
   <si>
     <t>Settings.Help</t>
   </si>
   <si>
-    <t>Help/Feedback</t>
+    <t>帮助/反馈</t>
   </si>
   <si>
     <t>Settings.Language</t>
   </si>
   <si>
-    <t>language</t>
+    <t>语言</t>
   </si>
   <si>
     <t>Settings.Music</t>
   </si>
   <si>
-    <t>background music</t>
+    <t>背景音乐</t>
   </si>
   <si>
     <t>Settings.Privacy</t>
   </si>
   <si>
-    <t>Privacy Agreement</t>
+    <t>隐私协议</t>
   </si>
   <si>
     <t>Settings.Rating</t>
   </si>
   <si>
-    <t>score</t>
+    <t>评分</t>
   </si>
   <si>
     <t>Settings.SFX</t>
   </si>
   <si>
-    <t>Sound effects</t>
+    <t>音效</t>
   </si>
   <si>
     <t>Settings.Title</t>
   </si>
   <si>
-    <t>set up</t>
+    <t>设置</t>
   </si>
   <si>
     <t>Settings.Vibrate</t>
   </si>
   <si>
-    <t>shock</t>
+    <t>震动</t>
   </si>
   <si>
     <t>SHOP</t>
   </si>
   <si>
-    <t>Shop</t>
+    <t>商店</t>
   </si>
   <si>
     <t>STEERING</t>
   </si>
   <si>
-    <t>drive</t>
+    <t>驾驶</t>
   </si>
   <si>
     <t>SuccessGame</t>
   </si>
   <si>
-    <t>You successfully captured the heart of the boss's daughter, immediately married Bai Fumei, and embarked on the peak of your life from then on</t>
+    <t>你成功俘获了老板女儿的芳心，立刻迎娶了白富美，从此走向人生巅峰</t>
   </si>
   <si>
     <t>TermsOfService</t>
   </si>
   <si>
-    <t>Service Terms</t>
+    <t>服务条款</t>
   </si>
   <si>
     <t>Test123</t>
   </si>
   <si>
-    <t>Code testing language scanning</t>
+    <t>代码测试语言扫描</t>
   </si>
   <si>
     <t>TipStart</t>
   </si>
   <si>
-    <t>Click on Xiaoming to kiss, but be careful if the boss sees it! Pay attention to the doors and windows!</t>
+    <t>点击小明小美亲吻，但是小心老板看见！ 另外注意门和窗户啦！</t>
   </si>
   <si>
     <t>UNLOCK</t>
   </si>
   <si>
-    <t>Unlock</t>
+    <t>解锁</t>
   </si>
 </sst>
 </file>
@@ -756,154 +753,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="0" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -968,148 +965,428 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" noThreeD="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -1124,50 +1401,69 @@
           <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1061" name="A1" hidden="1">
+            <xdr:cNvPr hidden="1" name="A1" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1061"/>
+                  <a14:compatExt spid="_x0000_s1060"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1191,50 +1487,69 @@
           <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1062" name="A2" hidden="1">
+            <xdr:cNvPr hidden="1" name="A2" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1062"/>
+                  <a14:compatExt spid="_x0000_s1061"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="190500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1258,50 +1573,69 @@
           <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1063" name="A3" hidden="1">
+            <xdr:cNvPr hidden="1" name="A3" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1063"/>
+                  <a14:compatExt spid="_x0000_s1062"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="381000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1325,50 +1659,69 @@
           <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1064" name="A4" hidden="1">
+            <xdr:cNvPr hidden="1" name="A4" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1064"/>
+                  <a14:compatExt spid="_x0000_s1063"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="571500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1392,50 +1745,69 @@
           <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1065" name="A5" hidden="1">
+            <xdr:cNvPr hidden="1" name="A5" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1065"/>
+                  <a14:compatExt spid="_x0000_s1064"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="762000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1459,50 +1831,69 @@
           <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1066" name="A6" hidden="1">
+            <xdr:cNvPr hidden="1" name="A6" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1066"/>
+                  <a14:compatExt spid="_x0000_s1065"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="952500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1526,50 +1917,69 @@
           <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1067" name="A7" hidden="1">
+            <xdr:cNvPr hidden="1" name="A7" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1067"/>
+                  <a14:compatExt spid="_x0000_s1066"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="1143000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1593,50 +2003,69 @@
           <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1068" name="A8" hidden="1">
+            <xdr:cNvPr hidden="1" name="A8" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1068"/>
+                  <a14:compatExt spid="_x0000_s1067"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="1333500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1660,50 +2089,69 @@
           <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1069" name="A9" hidden="1">
+            <xdr:cNvPr hidden="1" name="A9" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1069"/>
+                  <a14:compatExt spid="_x0000_s1068"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="1524000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1727,50 +2175,69 @@
           <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1070" name="A10" hidden="1">
+            <xdr:cNvPr hidden="1" name="A10" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
+                  <a14:compatExt spid="_x0000_s1069"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="1714500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1794,50 +2261,69 @@
           <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1071" name="A11" hidden="1">
+            <xdr:cNvPr hidden="1" name="A11" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1071"/>
+                  <a14:compatExt spid="_x0000_s1070"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="1905000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1861,50 +2347,69 @@
           <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1072" name="A12" hidden="1">
+            <xdr:cNvPr hidden="1" name="A12" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1072"/>
+                  <a14:compatExt spid="_x0000_s1071"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="2095500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1928,50 +2433,69 @@
           <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1073" name="A13" hidden="1">
+            <xdr:cNvPr hidden="1" name="A13" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1073"/>
+                  <a14:compatExt spid="_x0000_s1072"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="2286000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1995,50 +2519,69 @@
           <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1074" name="A14" hidden="1">
+            <xdr:cNvPr hidden="1" name="A14" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1074"/>
+                  <a14:compatExt spid="_x0000_s1073"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="2476500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2062,50 +2605,69 @@
           <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1075" name="A15" hidden="1">
+            <xdr:cNvPr hidden="1" name="A15" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1075"/>
+                  <a14:compatExt spid="_x0000_s1074"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="2667000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2129,50 +2691,69 @@
           <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1076" name="A16" hidden="1">
+            <xdr:cNvPr hidden="1" name="A16" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1076"/>
+                  <a14:compatExt spid="_x0000_s1075"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="2857500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2196,50 +2777,69 @@
           <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1077" name="A17" hidden="1">
+            <xdr:cNvPr hidden="1" name="A17" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1077"/>
+                  <a14:compatExt spid="_x0000_s1076"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="3048000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2263,50 +2863,69 @@
           <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1078" name="A18" hidden="1">
+            <xdr:cNvPr hidden="1" name="A18" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1078"/>
+                  <a14:compatExt spid="_x0000_s1077"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="3238500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2330,50 +2949,69 @@
           <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1079" name="A19" hidden="1">
+            <xdr:cNvPr hidden="1" name="A19" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1079"/>
+                  <a14:compatExt spid="_x0000_s1078"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="3429000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2397,50 +3035,69 @@
           <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1080" name="A20" hidden="1">
+            <xdr:cNvPr hidden="1" name="A20" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1080"/>
+                  <a14:compatExt spid="_x0000_s1079"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="3619500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2464,50 +3121,69 @@
           <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1081" name="A21" hidden="1">
+            <xdr:cNvPr hidden="1" name="A21" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1081"/>
+                  <a14:compatExt spid="_x0000_s1080"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="3810000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2531,50 +3207,69 @@
           <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1082" name="A22" hidden="1">
+            <xdr:cNvPr hidden="1" name="A22" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1082"/>
+                  <a14:compatExt spid="_x0000_s1081"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="4000500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2598,50 +3293,69 @@
           <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1083" name="A23" hidden="1">
+            <xdr:cNvPr hidden="1" name="A23" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1083"/>
+                  <a14:compatExt spid="_x0000_s1082"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="4191000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2665,50 +3379,69 @@
           <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1084" name="A24" hidden="1">
+            <xdr:cNvPr hidden="1" name="A24" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1084"/>
+                  <a14:compatExt spid="_x0000_s1083"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="4381500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2732,50 +3465,69 @@
           <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1085" name="A25" hidden="1">
+            <xdr:cNvPr hidden="1" name="A25" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1085"/>
+                  <a14:compatExt spid="_x0000_s1084"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="4572000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2799,50 +3551,69 @@
           <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1086" name="A26" hidden="1">
+            <xdr:cNvPr hidden="1" name="A26" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1086"/>
+                  <a14:compatExt spid="_x0000_s1085"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="4762500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2866,50 +3637,69 @@
           <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1087" name="A27" hidden="1">
+            <xdr:cNvPr hidden="1" name="A27" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1087"/>
+                  <a14:compatExt spid="_x0000_s1086"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="4953000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2933,50 +3723,69 @@
           <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1088" name="A28" hidden="1">
+            <xdr:cNvPr hidden="1" name="A28" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1088"/>
+                  <a14:compatExt spid="_x0000_s1087"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="5143500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -3000,50 +3809,69 @@
           <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1089" name="A29" hidden="1">
+            <xdr:cNvPr hidden="1" name="A29" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1089"/>
+                  <a14:compatExt spid="_x0000_s1088"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="5334000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -3067,50 +3895,69 @@
           <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1090" name="A30" hidden="1">
+            <xdr:cNvPr hidden="1" name="A30" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1090"/>
+                  <a14:compatExt spid="_x0000_s1089"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="5524500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -3134,50 +3981,69 @@
           <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1091" name="A31" hidden="1">
+            <xdr:cNvPr hidden="1" name="A31" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1091"/>
+                  <a14:compatExt spid="_x0000_s1090"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="5715000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -3201,50 +4067,69 @@
           <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1092" name="A32" hidden="1">
+            <xdr:cNvPr hidden="1" name="A32" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1092"/>
+                  <a14:compatExt spid="_x0000_s1091"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="5905500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -3268,50 +4153,69 @@
           <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1093" name="A33" hidden="1">
+            <xdr:cNvPr hidden="1" name="A33" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1093"/>
+                  <a14:compatExt spid="_x0000_s1092"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="6096000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -3335,50 +4239,69 @@
           <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1094" name="A34" hidden="1">
+            <xdr:cNvPr hidden="1" name="A34" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="6286500"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -3402,50 +4325,69 @@
           <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1095" name="A35" hidden="1">
+            <xdr:cNvPr hidden="1" name="A35" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
+                  <a14:compatExt spid="_x0000_s1094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="0" y="6477000"/>
-              <a:ext cx="285750" cy="190500"/>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="l" rtl="0">
+              <a:pPr rtl="0" algn="l">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
-                  <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                  <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
                 </a:rPr>
                 <a:t>锁定</a:t>
               </a:r>
-              <a:endParaRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Segoe UI" panose="020B0502040204020203"/>
-                <a:cs typeface="Segoe UI" panose="020B0502040204020203"/>
-              </a:endParaRPr>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -3719,322 +4661,322 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="25.4095238095238" customWidth="1"/>
+    <col min="2" max="2" width="25.4074859619141" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1">
       <c r="A1" s="1"/>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2">
       <c r="A2" s="1"/>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3">
       <c r="A3" s="1"/>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4">
       <c r="A4" s="1"/>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5">
       <c r="A5" s="1"/>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6">
       <c r="A6" s="1"/>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7">
       <c r="A7" s="1"/>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8">
       <c r="A8" s="1"/>
-      <c r="B8" t="s">
+      <c r="B8" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9">
       <c r="A9" s="1"/>
-      <c r="B9" t="s">
+      <c r="B9" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10">
       <c r="A10" s="1"/>
-      <c r="B10" t="s">
+      <c r="B10" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="0" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11">
       <c r="A11" s="1"/>
-      <c r="B11" t="s">
+      <c r="B11" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="0" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12">
       <c r="A12" s="1"/>
-      <c r="B12" t="s">
+      <c r="B12" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="0" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13">
       <c r="A13" s="1"/>
-      <c r="B13" t="s">
+      <c r="B13" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="0" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14">
       <c r="A14" s="1"/>
-      <c r="B14" t="s">
+      <c r="B14" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="0" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15">
       <c r="A15" s="1"/>
-      <c r="B15" t="s">
+      <c r="B15" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="0" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16">
       <c r="A16" s="1"/>
-      <c r="B16" t="s">
+      <c r="B16" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="0" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17">
       <c r="A17" s="1"/>
-      <c r="B17" t="s">
+      <c r="B17" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="0" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18">
       <c r="A18" s="1"/>
-      <c r="B18" t="s">
+      <c r="B18" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="0" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19">
       <c r="A19" s="1"/>
-      <c r="B19" t="s">
+      <c r="B19" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="0" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20">
       <c r="A20" s="1"/>
-      <c r="B20" t="s">
+      <c r="B20" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="0" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21">
       <c r="A21" s="1"/>
-      <c r="B21" t="s">
+      <c r="B21" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="0" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22">
       <c r="A22" s="1"/>
-      <c r="B22" t="s">
+      <c r="B22" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="0" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23">
       <c r="A23" s="1"/>
-      <c r="B23" t="s">
+      <c r="B23" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="0" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24">
       <c r="A24" s="1"/>
-      <c r="B24" t="s">
+      <c r="B24" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="0" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25">
       <c r="A25" s="1"/>
-      <c r="B25" t="s">
+      <c r="B25" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="0" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26">
       <c r="A26" s="1"/>
-      <c r="B26" t="s">
+      <c r="B26" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="0" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27">
       <c r="A27" s="1"/>
-      <c r="B27" t="s">
+      <c r="B27" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="0" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28">
       <c r="A28" s="1"/>
-      <c r="B28" t="s">
+      <c r="B28" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="0" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29">
       <c r="A29" s="1"/>
-      <c r="B29" t="s">
+      <c r="B29" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="0" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30">
       <c r="A30" s="1"/>
-      <c r="B30" t="s">
+      <c r="B30" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="0" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31">
       <c r="A31" s="1"/>
-      <c r="B31" t="s">
+      <c r="B31" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="0" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32">
       <c r="A32" s="1"/>
-      <c r="B32" t="s">
+      <c r="B32" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="0" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33">
       <c r="A33" s="1"/>
-      <c r="B33" t="s">
+      <c r="B33" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="0" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34">
       <c r="A34" s="1"/>
-      <c r="B34" t="s">
+      <c r="B34" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="0" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35">
       <c r="A35" s="1"/>
-      <c r="B35" t="s">
+      <c r="B35" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="0" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4047,10 +4989,10 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" name="A1" r:id="rId4">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1060" r:id="rId72" name="A1">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4069,10 +5011,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" name="A2" r:id="rId5">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1061" r:id="rId73" name="A2">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4091,10 +5033,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" name="A3" r:id="rId6">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1062" r:id="rId74" name="A3">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4113,10 +5055,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" name="A4" r:id="rId7">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1063" r:id="rId75" name="A4">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4135,10 +5077,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" name="A5" r:id="rId8">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1064" r:id="rId76" name="A5">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4157,10 +5099,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" name="A6" r:id="rId9">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1065" r:id="rId77" name="A6">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4179,10 +5121,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" name="A7" r:id="rId10">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1066" r:id="rId78" name="A7">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4201,10 +5143,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" name="A8" r:id="rId11">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1067" r:id="rId79" name="A8">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4223,10 +5165,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" name="A9" r:id="rId12">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1068" r:id="rId80" name="A9">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4245,10 +5187,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" name="A10" r:id="rId13">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1069" r:id="rId81" name="A10">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4267,10 +5209,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" name="A11" r:id="rId14">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1070" r:id="rId82" name="A11">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4289,10 +5231,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" name="A12" r:id="rId15">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1071" r:id="rId83" name="A12">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4311,10 +5253,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" name="A13" r:id="rId16">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1072" r:id="rId84" name="A13">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4333,10 +5275,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" name="A14" r:id="rId17">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1073" r:id="rId85" name="A14">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4355,10 +5297,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" name="A15" r:id="rId18">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1074" r:id="rId86" name="A15">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4377,10 +5319,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" name="A16" r:id="rId19">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1075" r:id="rId87" name="A16">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4399,10 +5341,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" name="A17" r:id="rId20">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1076" r:id="rId88" name="A17">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4421,10 +5363,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" name="A18" r:id="rId21">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1077" r:id="rId89" name="A18">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4443,10 +5385,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" name="A19" r:id="rId22">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1078" r:id="rId90" name="A19">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4465,10 +5407,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" name="A20" r:id="rId23">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1079" r:id="rId91" name="A20">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4487,10 +5429,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" name="A21" r:id="rId24">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1080" r:id="rId92" name="A21">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4509,10 +5451,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" name="A22" r:id="rId25">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1081" r:id="rId93" name="A22">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4531,10 +5473,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" name="A23" r:id="rId26">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1082" r:id="rId94" name="A23">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4553,10 +5495,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" name="A24" r:id="rId27">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1083" r:id="rId95" name="A24">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4575,10 +5517,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" name="A25" r:id="rId28">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1084" r:id="rId96" name="A25">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4597,10 +5539,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" name="A26" r:id="rId29">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1085" r:id="rId97" name="A26">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4619,10 +5561,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" name="A27" r:id="rId30">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1086" r:id="rId98" name="A27">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4641,10 +5583,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" name="A28" r:id="rId31">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1087" r:id="rId99" name="A28">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4663,10 +5605,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" name="A29" r:id="rId32">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1088" r:id="rId100" name="A29">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4685,10 +5627,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" name="A30" r:id="rId33">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1089" r:id="rId101" name="A30">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4707,10 +5649,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" name="A31" r:id="rId34">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1090" r:id="rId102" name="A31">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4729,10 +5671,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" name="A32" r:id="rId35">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1091" r:id="rId103" name="A32">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4751,10 +5693,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" name="A33" r:id="rId36">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1092" r:id="rId104" name="A33">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4773,10 +5715,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" name="A34" r:id="rId37">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1093" r:id="rId105" name="A34">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
@@ -4795,10 +5737,10 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" name="A35" r:id="rId38">
-              <controlPr print="0" defaultSize="0">
+            <control shapeId="1094" r:id="rId106" name="A35">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>0</xdr:col>
